--- a/01_Attendance/業務フロー（改善後）.xlsx
+++ b/01_Attendance/業務フロー（改善後）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yu-sugino\Downloads\workspace\14_extratask\01_Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7325EE-FDA4-4936-AF82-C8777648C6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555CAC7F-E88E-4D35-9668-D321C1907344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{CC92D52B-6FEE-4178-85E7-11D7EE1410EB}"/>
   </bookViews>
@@ -131,16 +131,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>609731</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>272452</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>125343</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>526474</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>180108</xdr:rowOff>
+      <xdr:rowOff>150326</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>189195</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>37475</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -155,8 +155,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1939767" y="125343"/>
-          <a:ext cx="1911798" cy="761347"/>
+          <a:off x="2296124" y="150326"/>
+          <a:ext cx="1940415" cy="786559"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -203,16 +203,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>617602</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>103454</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>574261</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>176696</xdr:rowOff>
+      <xdr:colOff>230357</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>115946</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>187016</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>189188</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -227,8 +227,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="617602" y="1263019"/>
-          <a:ext cx="1977616" cy="768981"/>
+          <a:off x="2254029" y="4163290"/>
+          <a:ext cx="1980331" cy="747800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -304,16 +304,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>582575</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>137501</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>585303</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>187738</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>195330</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>174977</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>198057</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>361</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -328,8 +328,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="582575" y="2456631"/>
-          <a:ext cx="2023685" cy="745977"/>
+          <a:off x="869887" y="5571436"/>
+          <a:ext cx="2026400" cy="724794"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -381,16 +381,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>547548</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>54446</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>596348</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>154609</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>160303</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>91922</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>209102</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>192084</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -405,8 +405,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="547548" y="3533142"/>
-          <a:ext cx="2069757" cy="795902"/>
+          <a:off x="834860" y="6612643"/>
+          <a:ext cx="2072472" cy="774720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -458,16 +458,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>453387</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>218465</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>528710</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>135535</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>66142</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>31088</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>141465</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>173011</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -482,8 +482,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1783423" y="4929010"/>
-          <a:ext cx="2070378" cy="1330234"/>
+          <a:off x="2089814" y="7900924"/>
+          <a:ext cx="2098995" cy="1266185"/>
         </a:xfrm>
         <a:prstGeom prst="diamond">
           <a:avLst/>
@@ -528,16 +528,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>446845</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>116164</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>519045</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>187739</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>47108</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>137409</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>119308</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>224851</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -552,8 +552,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3141454" y="1275729"/>
-          <a:ext cx="2093156" cy="767314"/>
+          <a:off x="3419895" y="4409606"/>
+          <a:ext cx="2095872" cy="761999"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -629,16 +629,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>422548</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>124998</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>519043</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>187739</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>35303</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>162474</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>131798</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>362</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -653,8 +653,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3117157" y="2444128"/>
-          <a:ext cx="2117451" cy="758481"/>
+          <a:off x="3408090" y="5558933"/>
+          <a:ext cx="2120167" cy="737298"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -778,16 +778,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>398254</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>100702</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>519044</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>154609</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>11009</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>138178</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>131799</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>192084</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -802,8 +802,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3092863" y="3579398"/>
-          <a:ext cx="2141746" cy="749646"/>
+          <a:off x="3383796" y="6658899"/>
+          <a:ext cx="2144462" cy="728464"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -927,16 +927,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>528710</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>177000</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>141465</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>214476</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>376081</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>179708</xdr:rowOff>
+      <xdr:colOff>663393</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>217184</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -954,8 +954,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3853801" y="5594127"/>
-          <a:ext cx="1177407" cy="2708"/>
+          <a:off x="4188809" y="8534017"/>
+          <a:ext cx="1196486" cy="2708"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -984,9 +984,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>190751</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>201795</xdr:rowOff>
+      <xdr:colOff>490554</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>126844</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="374013" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -1002,7 +1002,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4180860" y="5383395"/>
+          <a:off x="4537898" y="8221533"/>
           <a:ext cx="374013" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1043,15 +1043,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>368739</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>31631</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>491736</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>54616</xdr:rowOff>
+      <xdr:colOff>656051</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>69106</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>104491</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>92091</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1066,8 +1066,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5023866" y="5213231"/>
-          <a:ext cx="2118052" cy="729567"/>
+          <a:off x="5377953" y="8163795"/>
+          <a:ext cx="2146669" cy="697542"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1237,15 +1237,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>363720</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>156923</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>486717</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>179908</xdr:rowOff>
+      <xdr:colOff>651032</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>194398</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>99472</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>217384</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1260,8 +1260,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5018847" y="7929323"/>
-          <a:ext cx="2118052" cy="729567"/>
+          <a:off x="5372934" y="10762464"/>
+          <a:ext cx="2146669" cy="697543"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1323,15 +1323,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>364636</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>157421</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>486114</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>190552</xdr:rowOff>
+      <xdr:colOff>651948</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>194896</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>98869</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>3175</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1346,8 +1346,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5019763" y="6516657"/>
-          <a:ext cx="2116533" cy="739713"/>
+          <a:off x="5373850" y="9413847"/>
+          <a:ext cx="2145150" cy="707689"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartPredefinedProcess">
           <a:avLst/>
@@ -1400,15 +1400,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>330789</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>21189</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>453787</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>44174</xdr:rowOff>
+      <xdr:colOff>618101</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>58664</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>66541</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>81649</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1423,8 +1423,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7645989" y="5202789"/>
-          <a:ext cx="2118053" cy="729567"/>
+          <a:off x="8038232" y="8153353"/>
+          <a:ext cx="2146670" cy="697542"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1593,16 +1593,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>403991</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>82927</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>525469</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>119673</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>16746</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>120403</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>138224</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>157148</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1617,8 +1617,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1734027" y="9268491"/>
-          <a:ext cx="2116533" cy="743327"/>
+          <a:off x="2040418" y="12037583"/>
+          <a:ext cx="2145150" cy="711303"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartPredefinedProcess">
           <a:avLst/>
@@ -1702,16 +1702,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>542021</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>44883</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>154776</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>82359</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>60248</xdr:rowOff>
+      <xdr:colOff>287312</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>97724</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1726,8 +1726,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1872057" y="10643610"/>
-          <a:ext cx="2118052" cy="721947"/>
+          <a:off x="2178448" y="13348654"/>
+          <a:ext cx="2156208" cy="689922"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1824,16 +1824,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>543540</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>191162</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>156295</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>3785</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>287312</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>37476</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1848,8 +1848,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1873576" y="11967526"/>
-          <a:ext cx="2116533" cy="750947"/>
+          <a:off x="2179967" y="14619195"/>
+          <a:ext cx="2154689" cy="708248"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartPredefinedProcess">
           <a:avLst/>
@@ -1902,15 +1902,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>196572</xdr:rowOff>
+      <xdr:colOff>287312</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>9195</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>121479</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>229703</xdr:rowOff>
+      <xdr:colOff>408791</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>42326</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1925,8 +1925,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10640291" y="4436063"/>
-          <a:ext cx="2116533" cy="739713"/>
+          <a:off x="11080230" y="7429326"/>
+          <a:ext cx="2145151" cy="707689"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartPredefinedProcess">
           <a:avLst/>
@@ -1978,16 +1978,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>543540</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>156295</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>37476</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>44365</xdr:rowOff>
+      <xdr:colOff>287312</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>81840</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2002,8 +2002,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1873576" y="13189527"/>
-          <a:ext cx="2116533" cy="750947"/>
+          <a:off x="2179967" y="15777148"/>
+          <a:ext cx="2154689" cy="718922"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartPredefinedProcess">
           <a:avLst/>
@@ -2055,16 +2055,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>595876</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>180762</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>208631</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>218238</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>287312</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>37475</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2079,8 +2079,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1925912" y="14312398"/>
-          <a:ext cx="2064197" cy="761347"/>
+          <a:off x="2232303" y="16857320"/>
+          <a:ext cx="2102353" cy="718647"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -2128,15 +2128,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>132221</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>135535</xdr:rowOff>
+      <xdr:colOff>414763</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>173011</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>158539</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>82927</xdr:rowOff>
+      <xdr:colOff>441082</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>120403</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2155,8 +2155,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="2792294" y="6259244"/>
-          <a:ext cx="26318" cy="3009247"/>
+          <a:off x="3112993" y="9167109"/>
+          <a:ext cx="26319" cy="2870474"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2185,15 +2185,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>239440</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>154609</xdr:rowOff>
+      <xdr:colOff>526752</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>192084</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>374072</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>69273</xdr:rowOff>
+      <xdr:colOff>661384</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>106748</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2211,8 +2211,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1569476" y="4394100"/>
-          <a:ext cx="799651" cy="856773"/>
+          <a:off x="1875867" y="7387363"/>
+          <a:ext cx="809189" cy="814074"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2241,15 +2241,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>154609</xdr:rowOff>
+      <xdr:colOff>287312</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>192084</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>126140</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>69273</xdr:rowOff>
+      <xdr:colOff>413452</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>106748</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2267,8 +2267,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="3325091" y="4394100"/>
-          <a:ext cx="791158" cy="856773"/>
+          <a:off x="3660099" y="7387363"/>
+          <a:ext cx="800697" cy="814074"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2297,15 +2297,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>92866</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>54616</xdr:rowOff>
+      <xdr:colOff>375409</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>92091</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>97728</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>157421</xdr:rowOff>
+      <xdr:colOff>380272</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>194896</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2324,8 +2324,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="6078030" y="5942798"/>
-          <a:ext cx="4862" cy="573859"/>
+          <a:off x="6446425" y="8861337"/>
+          <a:ext cx="4863" cy="552510"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2354,15 +2354,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>92709</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>190552</xdr:rowOff>
+      <xdr:colOff>375253</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>3175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>92866</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>156923</xdr:rowOff>
+      <xdr:colOff>375409</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>194398</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2381,8 +2381,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="6077873" y="7256370"/>
-          <a:ext cx="157" cy="672953"/>
+          <a:off x="6446269" y="10121536"/>
+          <a:ext cx="156" cy="640928"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2410,16 +2410,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>525469</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>50652</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>138224</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>93466</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>363720</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>219064</xdr:rowOff>
+      <xdr:colOff>651032</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>26350</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2438,8 +2438,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="3850560" y="8294107"/>
-          <a:ext cx="1168287" cy="1346048"/>
+          <a:off x="4185568" y="11111236"/>
+          <a:ext cx="1187366" cy="1281999"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2468,15 +2468,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>132221</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>119673</xdr:rowOff>
+      <xdr:colOff>414763</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>157148</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>271010</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>44883</xdr:rowOff>
+      <xdr:colOff>558322</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>82359</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2495,8 +2495,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2792294" y="10011818"/>
-          <a:ext cx="138789" cy="631792"/>
+          <a:off x="3112993" y="12748886"/>
+          <a:ext cx="143559" cy="599768"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2524,16 +2524,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>491736</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>150446</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>330789</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>160888</xdr:rowOff>
+      <xdr:colOff>104491</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>182583</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>618101</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>193025</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2552,8 +2552,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="7141918" y="5567573"/>
-          <a:ext cx="504071" cy="10442"/>
+          <a:off x="7524622" y="8502124"/>
+          <a:ext cx="513610" cy="10442"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2581,16 +2581,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>596348</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>222292</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>209102</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>29577</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>95375</xdr:rowOff>
+      <xdr:colOff>287312</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>138187</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2608,12 +2608,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2591403" y="3990728"/>
-          <a:ext cx="8048888" cy="815192"/>
+          <a:off x="2907332" y="7000003"/>
+          <a:ext cx="8172898" cy="783168"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 3525"/>
+            <a:gd name="adj1" fmla="val 2924"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -2639,16 +2639,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>519044</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>9892</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>131799</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>52705</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>95375</xdr:rowOff>
+      <xdr:colOff>287312</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>138187</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2666,8 +2666,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5174171" y="4013856"/>
-          <a:ext cx="5466120" cy="792064"/>
+          <a:off x="5528258" y="7023131"/>
+          <a:ext cx="5551972" cy="760040"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
@@ -2697,16 +2697,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>453787</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>229703</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>393249</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>150446</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>66541</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>42326</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>10773</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>182583</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2724,8 +2724,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="9764042" y="5175776"/>
-          <a:ext cx="1934516" cy="391797"/>
+          <a:off x="10184902" y="8137015"/>
+          <a:ext cx="1967904" cy="365109"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector2">
           <a:avLst/>
@@ -2753,16 +2753,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>525469</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>95375</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>138224</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>138187</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>121479</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>219064</xdr:rowOff>
+      <xdr:colOff>408791</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>26350</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2780,12 +2780,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="3850560" y="4805920"/>
-          <a:ext cx="8906264" cy="4834235"/>
+          <a:off x="4185568" y="7783171"/>
+          <a:ext cx="9039813" cy="4610064"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -2567"/>
+            <a:gd name="adj1" fmla="val -2529"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -2812,15 +2812,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>271010</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>60248</xdr:rowOff>
+      <xdr:colOff>558322</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>97724</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>271770</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>191162</xdr:rowOff>
+      <xdr:colOff>559082</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>3785</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2839,8 +2839,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2931083" y="11365557"/>
-          <a:ext cx="760" cy="601969"/>
+          <a:off x="3256552" y="14038576"/>
+          <a:ext cx="760" cy="580619"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2869,15 +2869,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>271770</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>559082</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>37476</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>271770</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>559082</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>37476</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2896,8 +2896,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2931843" y="12718473"/>
-          <a:ext cx="0" cy="471054"/>
+          <a:off x="3257312" y="15327443"/>
+          <a:ext cx="0" cy="449705"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2926,15 +2926,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>271770</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>44365</xdr:rowOff>
+      <xdr:colOff>559082</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>81840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>297938</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>180762</xdr:rowOff>
+      <xdr:colOff>585250</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>218238</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2953,8 +2953,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2931843" y="13940474"/>
-          <a:ext cx="26168" cy="371924"/>
+          <a:off x="3257312" y="16496070"/>
+          <a:ext cx="26168" cy="361250"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2983,15 +2983,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>239440</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>187738</xdr:rowOff>
+      <xdr:colOff>521981</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>361</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>251431</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>54446</xdr:rowOff>
+      <xdr:colOff>533972</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>91922</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3010,8 +3010,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="1569476" y="3249593"/>
-          <a:ext cx="11991" cy="337762"/>
+          <a:off x="1871096" y="6296230"/>
+          <a:ext cx="11991" cy="316413"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3040,15 +3040,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>126140</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>187739</xdr:rowOff>
+      <xdr:colOff>408683</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>362</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>138287</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>100702</xdr:rowOff>
+      <xdr:colOff>420830</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>138178</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3067,8 +3067,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="4116249" y="3249594"/>
-          <a:ext cx="12147" cy="384017"/>
+          <a:off x="4456027" y="6296231"/>
+          <a:ext cx="12147" cy="362668"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3097,15 +3097,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>138287</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>187739</xdr:rowOff>
+      <xdr:colOff>420487</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>224851</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>150436</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>124998</xdr:rowOff>
+      <xdr:colOff>420830</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>162474</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3123,9 +3123,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="4128396" y="2071957"/>
-          <a:ext cx="12149" cy="408314"/>
+        <a:xfrm>
+          <a:off x="4467831" y="5171605"/>
+          <a:ext cx="343" cy="387328"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3153,38 +3153,37 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>251431</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>176696</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>263423</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>137501</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>187016</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>40141</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>134690</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>57206</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="131" name="直線矢印コネクタ 130">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B53C92A2-D236-41EA-B368-549457E2C815}"/>
+        <xdr:cNvPr id="134" name="コネクタ: カギ線 133">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B7136B1-7505-4854-829C-E0F7F03C618B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:cxnSpLocks/>
-          <a:stCxn id="3" idx="2"/>
-          <a:endCxn id="4" idx="0"/>
+          <a:stCxn id="3" idx="3"/>
+          <a:endCxn id="10" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="1581467" y="2060914"/>
-          <a:ext cx="11992" cy="431860"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
+        <a:xfrm>
+          <a:off x="4234360" y="4537190"/>
+          <a:ext cx="2645904" cy="466770"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
           <a:avLst/>
         </a:prstGeom>
         <a:ln>
@@ -3208,124 +3207,12 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>526474</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>34962</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>150436</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>116164</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="134" name="コネクタ: カギ線 133">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B7136B1-7505-4854-829C-E0F7F03C618B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="2" idx="3"/>
-          <a:endCxn id="7" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3851565" y="506017"/>
-          <a:ext cx="288980" cy="787783"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector2">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>263423</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>34961</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>609731</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>103453</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="137" name="コネクタ: カギ線 136">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FA9AA41-D006-4BEB-AEEB-BE638EB06A76}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="2" idx="1"/>
-          <a:endCxn id="3" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="10800000" flipV="1">
-          <a:off x="1593459" y="506016"/>
-          <a:ext cx="346308" cy="775073"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector2">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>374072</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>12532</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>24301</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>40</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="327397" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -3341,7 +3228,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2369127" y="7313877"/>
+          <a:off x="2722531" y="9893548"/>
           <a:ext cx="327397" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3378,6 +3265,900 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>434307</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>57206</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>509630</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>149901</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="ひし形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D083A6F-7E50-4536-BAF2-0FED7E5F8334}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5830766" y="5003960"/>
+          <a:ext cx="2098995" cy="1216957"/>
+        </a:xfrm>
+        <a:prstGeom prst="diamond">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>IC</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>カードは登録済みか？</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>186970</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>84690</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>262293</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>177385</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="65" name="ひし形 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93A6ECEC-D062-4FDA-894E-D641C5F908B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2210642" y="1433805"/>
+          <a:ext cx="2098995" cy="1216957"/>
+        </a:xfrm>
+        <a:prstGeom prst="diamond">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>システムにアカウント登録済みか？</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>237344</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>93460</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>194003</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>166702</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="72" name="正方形/長方形 71">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03202494-FD51-47B1-BA11-312895AFA3CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2261016" y="3016542"/>
+          <a:ext cx="1980331" cy="747799"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="10000"/>
+            <a:lumOff val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900" b="0" cap="none" spc="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>従業員がスマホや</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900" b="0" cap="none" spc="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>PC</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900" b="0" cap="none" spc="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>、で勤怠システムへアカウント登録</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>545965</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>166702</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>552952</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>115946</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="74" name="直線矢印コネクタ 73">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2408840B-C3D1-494F-AE91-C1D51D1A9DB3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="72" idx="2"/>
+          <a:endCxn id="3" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3244195" y="3764341"/>
+          <a:ext cx="6987" cy="398949"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>552952</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>177385</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>561910</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>93460</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="78" name="直線矢印コネクタ 77">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76EFDE2B-6279-473F-B1E8-8754731A3DC4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="65" idx="2"/>
+          <a:endCxn id="72" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3251182" y="2650762"/>
+          <a:ext cx="8958" cy="365780"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>186969</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>18612</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>230356</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>40141</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="83" name="コネクタ: カギ線 82">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBE9DEC9-A3AA-4390-84C5-50E3E02864FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="65" idx="1"/>
+          <a:endCxn id="3" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipH="1" flipV="1">
+          <a:off x="2210641" y="2042284"/>
+          <a:ext cx="43387" cy="2494906"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -843594"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>131798</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>215980</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>509630</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>81418</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="86" name="コネクタ: カギ線 85">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58C9F5C5-CADE-4FDC-B547-3975B63BAFB5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="10" idx="3"/>
+          <a:endCxn id="8" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="5528257" y="5612439"/>
+          <a:ext cx="2401504" cy="2338815"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -9519"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>624591</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>24984</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="374013" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="96" name="テキスト ボックス 95">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92779CEE-C494-4E2C-B53F-9BC812A88FD1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1299148" y="2723214"/>
+          <a:ext cx="374013" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>yes</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>249837</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>12490</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="374013" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="97" name="テキスト ボックス 96">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08F8B756-2F8C-4BDC-B84F-D4053AB61616}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7669968" y="6308359"/>
+          <a:ext cx="374013" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>yes</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>12492</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>174885</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="327397" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="98" name="テキスト ボックス 97">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A71D1FAD-9CAF-42B7-906E-9F679721A98C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3385279" y="2648262"/>
+          <a:ext cx="327397" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>no</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>437213</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>74950</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="327397" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="99" name="テキスト ボックス 98">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81933412-1F92-49A6-B2BA-86B9301DCB78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5159115" y="5246557"/>
+          <a:ext cx="327397" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>no</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>561910</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>37475</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>568102</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>84690</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="108" name="直線矢印コネクタ 107">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7C679A5-39E7-4826-9E12-12F28DB4FFA5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="2" idx="2"/>
+          <a:endCxn id="65" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3260140" y="936885"/>
+          <a:ext cx="6192" cy="496920"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>533972</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>189188</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>545965</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>174977</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="139" name="コネクタ: カギ線 138">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBF67EE0-7CC1-4379-9AC6-099075E2190D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="3" idx="2"/>
+          <a:endCxn id="4" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="1221632" y="5572545"/>
+          <a:ext cx="2684018" cy="1361108"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>420488</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>215979</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>434308</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>137408</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="143" name="コネクタ: カギ線 142">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{421E90B7-EF70-4F6C-B2D8-AA8D09CAF45B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="10" idx="1"/>
+          <a:endCxn id="7" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="4467832" y="5612438"/>
+          <a:ext cx="1362935" cy="820839"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3698,11 +4479,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10D1DD26-8B33-4CE9-AA3B-B8B909A94D3D}">
-  <dimension ref="H2"/>
+  <dimension ref="H3"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="8:8" x14ac:dyDescent="0.45">
-      <c r="H2" s="1" t="s">
+    <row r="3" spans="8:8" x14ac:dyDescent="0.45">
+      <c r="H3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
